--- a/AAII_Financials/Yearly/VSNT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VSNT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>VSNT</t>
   </si>
@@ -864,8 +864,8 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>61000</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -995,8 +995,8 @@
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
-        <v>61000</v>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1023,7 +1023,7 @@
         <v>3060000</v>
       </c>
       <c r="G21" s="3">
-        <v>3341000</v>
+        <v>3402000</v>
       </c>
       <c r="H21" s="3">
         <v>0</v>
@@ -1319,8 +1319,8 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3">
-        <v>-61000</v>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
